--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
   <si>
     <t>Filename</t>
   </si>
@@ -808,763 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.4562,0.0246,0.0053,0.4730</t>
-  </si>
-  <si>
-    <t>0.0014,0.0008,0.0005,0.9991</t>
-  </si>
-  <si>
-    <t>0.6595,0.0038,0.0017,0.2922</t>
-  </si>
-  <si>
-    <t>0.0269,0.0029,0.0046,0.9813</t>
-  </si>
-  <si>
-    <t>0.9947,0.0007,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9923,0.0003,0.0000,0.0023</t>
-  </si>
-  <si>
-    <t>0.9858,0.0005,0.0000,0.0052</t>
-  </si>
-  <si>
-    <t>0.9919,0.0003,0.0000,0.0026</t>
-  </si>
-  <si>
-    <t>0.9934,0.0008,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9943,0.0007,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9955,0.0001,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9951,0.0005,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.5958,0.0812,0.3064,0.0581</t>
-  </si>
-  <si>
-    <t>0.1430,0.0145,0.8217,0.0603</t>
-  </si>
-  <si>
-    <t>0.5528,0.0858,0.3803,0.0303</t>
-  </si>
-  <si>
-    <t>0.1480,0.0460,0.7863,0.0664</t>
-  </si>
-  <si>
-    <t>0.2832,0.0201,0.5299,0.2159</t>
-  </si>
-  <si>
-    <t>0.0010,0.9964,0.0238,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9941,0.0288,0.0000</t>
-  </si>
-  <si>
-    <t>0.0308,0.9493,0.0395,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.9972,0.0143,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9977,0.0247,0.0000</t>
-  </si>
-  <si>
-    <t>0.2191,0.0175,0.1804,0.5744</t>
-  </si>
-  <si>
-    <t>0.1480,0.3813,0.0930,0.6716</t>
-  </si>
-  <si>
-    <t>0.0071,0.0034,0.9838,0.0238</t>
-  </si>
-  <si>
-    <t>0.2887,0.1126,0.5300,0.0925</t>
-  </si>
-  <si>
-    <t>0.1741,0.0246,0.8133,0.0240</t>
-  </si>
-  <si>
-    <t>0.1519,0.0170,0.8222,0.0373</t>
-  </si>
-  <si>
-    <t>0.0025,0.0125,0.9919,0.0082</t>
-  </si>
-  <si>
-    <t>0.0219,0.9618,0.0466,0.0009</t>
-  </si>
-  <si>
-    <t>0.7322,0.0571,0.1840,0.0288</t>
-  </si>
-  <si>
-    <t>0.0006,0.0705,0.9970,0.0005</t>
-  </si>
-  <si>
-    <t>0.0072,0.9353,0.5006,0.0007</t>
-  </si>
-  <si>
-    <t>0.8685,0.0717,0.0169,0.0191</t>
-  </si>
-  <si>
-    <t>0.1294,0.6321,0.3995,0.0067</t>
-  </si>
-  <si>
-    <t>0.2539,0.7519,0.0185,0.0006</t>
-  </si>
-  <si>
-    <t>0.0081,0.9798,0.0584,0.0003</t>
-  </si>
-  <si>
-    <t>0.0053,0.9711,0.2244,0.0154</t>
-  </si>
-  <si>
-    <t>0.2044,0.1868,0.5507,0.1805</t>
-  </si>
-  <si>
-    <t>0.2903,0.0922,0.6227,0.0502</t>
-  </si>
-  <si>
-    <t>0.1102,0.0070,0.8423,0.0713</t>
-  </si>
-  <si>
-    <t>0.3152,0.0864,0.6280,0.0379</t>
-  </si>
-  <si>
-    <t>0.0015,0.9920,0.1036,0.0015</t>
-  </si>
-  <si>
-    <t>0.0121,0.0141,0.9463,0.1184</t>
-  </si>
-  <si>
-    <t>0.0825,0.3770,0.0255,0.8700</t>
-  </si>
-  <si>
-    <t>0.0026,0.9922,0.0427,0.0011</t>
-  </si>
-  <si>
-    <t>0.0022,0.9937,0.0298,0.0006</t>
-  </si>
-  <si>
-    <t>0.0015,0.9952,0.0264,0.0001</t>
-  </si>
-  <si>
-    <t>0.0298,0.0861,0.8989,0.0609</t>
-  </si>
-  <si>
-    <t>0.0210,0.8830,0.4843,0.0144</t>
-  </si>
-  <si>
-    <t>0.2669,0.0240,0.7257,0.0302</t>
-  </si>
-  <si>
-    <t>0.0244,0.0059,0.9700,0.0120</t>
-  </si>
-  <si>
-    <t>0.0008,0.0038,0.9959,0.0127</t>
-  </si>
-  <si>
-    <t>0.0740,0.6685,0.5417,0.0348</t>
-  </si>
-  <si>
-    <t>0.9505,0.0587,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.9925,0.0012,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9919,0.0047,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0060,0.2674,0.9668,0.0014</t>
-  </si>
-  <si>
-    <t>0.9911,0.0012,0.0000,0.0019</t>
-  </si>
-  <si>
-    <t>0.9932,0.0030,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9916,0.0021,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.0034,0.9636,0.4454,0.0022</t>
-  </si>
-  <si>
-    <t>0.0356,0.0961,0.9088,0.0366</t>
-  </si>
-  <si>
-    <t>0.0253,0.0118,0.9029,0.1708</t>
-  </si>
-  <si>
-    <t>0.0005,0.9804,0.6703,0.0002</t>
-  </si>
-  <si>
-    <t>0.0054,0.0066,0.9827,0.0337</t>
-  </si>
-  <si>
-    <t>0.0013,0.9960,0.0182,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.1192,0.0499,0.8715,0.0094</t>
-  </si>
-  <si>
-    <t>0.7228,0.0858,0.1367,0.0439</t>
-  </si>
-  <si>
-    <t>0.0006,0.1126,0.9964,0.0005</t>
-  </si>
-  <si>
-    <t>0.0154,0.8724,0.5947,0.0051</t>
-  </si>
-  <si>
-    <t>0.0078,0.9623,0.2786,0.0023</t>
-  </si>
-  <si>
-    <t>0.0008,0.9915,0.2350,0.0009</t>
-  </si>
-  <si>
-    <t>0.0008,0.9880,0.3932,0.0003</t>
-  </si>
-  <si>
-    <t>0.0030,0.0009,0.0034,0.9974</t>
-  </si>
-  <si>
-    <t>0.0012,0.0012,0.0006,0.9992</t>
-  </si>
-  <si>
-    <t>0.0008,0.0008,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0070,0.0018,0.0044,0.9944</t>
-  </si>
-  <si>
-    <t>0.0023,0.0014,0.0048,0.9975</t>
-  </si>
-  <si>
-    <t>0.0014,0.0019,0.0014,0.9989</t>
-  </si>
-  <si>
-    <t>0.0019,0.9840,0.2969,0.0020</t>
-  </si>
-  <si>
-    <t>0.0112,0.9265,0.4715,0.0058</t>
-  </si>
-  <si>
-    <t>0.0258,0.8879,0.4288,0.0184</t>
-  </si>
-  <si>
-    <t>0.0231,0.7922,0.6366,0.0100</t>
-  </si>
-  <si>
-    <t>0.0016,0.9627,0.6740,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.9881,0.2288,0.0009</t>
-  </si>
-  <si>
-    <t>0.9904,0.0008,0.0000,0.0027</t>
-  </si>
-  <si>
-    <t>0.9933,0.0032,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9888,0.0055,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9948,0.0008,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9871,0.0075,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9960,0.0004,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9953,0.0009,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9918,0.0032,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9954,0.0002,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9949,0.0003,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9956,0.0002,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9955,0.0008,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0003,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.0019,0.0023,0.9937,0.0229</t>
-  </si>
-  <si>
-    <t>0.0336,0.0154,0.9593,0.0093</t>
-  </si>
-  <si>
-    <t>0.4211,0.0603,0.1159,0.3285</t>
-  </si>
-  <si>
-    <t>0.3412,0.0110,0.6726,0.0296</t>
-  </si>
-  <si>
-    <t>0.0032,0.9929,0.0085,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9950,0.0256,0.0000</t>
-  </si>
-  <si>
-    <t>0.0406,0.9484,0.0135,0.0002</t>
-  </si>
-  <si>
-    <t>0.0173,0.9706,0.0232,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.9935,0.0197,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9972,0.0081,0.0000</t>
-  </si>
-  <si>
-    <t>0.2124,0.8008,0.0147,0.0006</t>
-  </si>
-  <si>
-    <t>0.3473,0.4771,0.1469,0.1291</t>
-  </si>
-  <si>
-    <t>0.3061,0.0290,0.6899,0.0296</t>
-  </si>
-  <si>
-    <t>0.2456,0.6489,0.0822,0.1378</t>
-  </si>
-  <si>
-    <t>0.2489,0.6604,0.1105,0.0858</t>
-  </si>
-  <si>
-    <t>0.0258,0.1478,0.0052,0.9615</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0151,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0122,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.9946,0.0228,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0395,0.0000</t>
-  </si>
-  <si>
-    <t>0.0086,0.9807,0.0347,0.0001</t>
-  </si>
-  <si>
-    <t>0.7439,0.2642,0.0168,0.0023</t>
-  </si>
-  <si>
-    <t>0.3653,0.6759,0.0118,0.0007</t>
-  </si>
-  <si>
-    <t>0.9555,0.0441,0.0027,0.0020</t>
-  </si>
-  <si>
-    <t>0.9879,0.0004,0.0000,0.0044</t>
-  </si>
-  <si>
-    <t>0.9872,0.0006,0.0000,0.0041</t>
-  </si>
-  <si>
-    <t>0.9918,0.0002,0.0000,0.0031</t>
-  </si>
-  <si>
-    <t>0.9941,0.0014,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9297,0.0824,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.9855,0.0005,0.0000,0.0056</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.6579,0.0811,0.0555,0.1442</t>
+  </si>
+  <si>
+    <t>0.0019,0.0009,0.0006,0.9988</t>
+  </si>
+  <si>
+    <t>0.3556,0.0062,0.0027,0.6522</t>
+  </si>
+  <si>
+    <t>0.0285,0.0035,0.0054,0.9811</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9964,0.0004,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9876,0.0011,0.0000,0.0032</t>
+  </si>
+  <si>
+    <t>0.9943,0.0003,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9924,0.0011,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9930,0.0023,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0003,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.2420,0.5902,0.2003,0.1106</t>
+  </si>
+  <si>
+    <t>0.0282,0.0839,0.9451,0.0081</t>
+  </si>
+  <si>
+    <t>0.4642,0.0341,0.5659,0.0213</t>
+  </si>
+  <si>
+    <t>0.0756,0.0415,0.8995,0.0168</t>
+  </si>
+  <si>
+    <t>0.5235,0.0780,0.3497,0.0826</t>
+  </si>
+  <si>
+    <t>0.0019,0.9931,0.0412,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.9906,0.0207,0.0000</t>
+  </si>
+  <si>
+    <t>0.0632,0.9204,0.0258,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9943,0.0268,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9975,0.0145,0.0000</t>
+  </si>
+  <si>
+    <t>0.3128,0.0323,0.2235,0.4099</t>
+  </si>
+  <si>
+    <t>0.4355,0.0740,0.2595,0.2326</t>
+  </si>
+  <si>
+    <t>0.0022,0.0027,0.9952,0.0055</t>
+  </si>
+  <si>
+    <t>0.3461,0.1631,0.3375,0.1972</t>
+  </si>
+  <si>
+    <t>0.3115,0.0072,0.6785,0.0375</t>
+  </si>
+  <si>
+    <t>0.0619,0.0247,0.8997,0.0486</t>
+  </si>
+  <si>
+    <t>0.0592,0.0270,0.9020,0.0586</t>
+  </si>
+  <si>
+    <t>0.0070,0.9845,0.0355,0.0004</t>
+  </si>
+  <si>
+    <t>0.6587,0.0619,0.3110,0.0164</t>
+  </si>
+  <si>
+    <t>0.0012,0.0161,0.9971,0.0013</t>
+  </si>
+  <si>
+    <t>0.0015,0.9842,0.3216,0.0001</t>
+  </si>
+  <si>
+    <t>0.8161,0.1132,0.0276,0.0255</t>
+  </si>
+  <si>
+    <t>0.0400,0.5126,0.7792,0.0041</t>
+  </si>
+  <si>
+    <t>0.6662,0.3820,0.0100,0.0010</t>
+  </si>
+  <si>
+    <t>0.0186,0.9632,0.0555,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.9811,0.0862,0.0503</t>
+  </si>
+  <si>
+    <t>0.2370,0.0249,0.6138,0.1401</t>
+  </si>
+  <si>
+    <t>0.2429,0.1536,0.5962,0.0848</t>
+  </si>
+  <si>
+    <t>0.1098,0.0119,0.8617,0.0448</t>
+  </si>
+  <si>
+    <t>0.1845,0.4311,0.5280,0.0778</t>
+  </si>
+  <si>
+    <t>0.0003,0.9975,0.0933,0.0003</t>
+  </si>
+  <si>
+    <t>0.0697,0.0451,0.8466,0.1199</t>
+  </si>
+  <si>
+    <t>0.0222,0.9240,0.0928,0.2341</t>
+  </si>
+  <si>
+    <t>0.0007,0.9974,0.0153,0.0020</t>
+  </si>
+  <si>
+    <t>0.0012,0.9962,0.0225,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9967,0.0489,0.0002</t>
+  </si>
+  <si>
+    <t>0.0222,0.0865,0.9292,0.0352</t>
+  </si>
+  <si>
+    <t>0.0080,0.7888,0.7910,0.0033</t>
+  </si>
+  <si>
+    <t>0.0599,0.0167,0.9203,0.0295</t>
+  </si>
+  <si>
+    <t>0.0633,0.0067,0.9268,0.0230</t>
+  </si>
+  <si>
+    <t>0.0282,0.0647,0.9174,0.0650</t>
+  </si>
+  <si>
+    <t>0.0562,0.6096,0.6556,0.0184</t>
+  </si>
+  <si>
+    <t>0.9430,0.0703,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9869,0.0021,0.0002,0.0034</t>
+  </si>
+  <si>
+    <t>0.9818,0.0014,0.0001,0.0062</t>
+  </si>
+  <si>
+    <t>0.0134,0.4325,0.9039,0.0023</t>
+  </si>
+  <si>
+    <t>0.9935,0.0012,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9963,0.0013,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9920,0.0027,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.0052,0.9598,0.3935,0.0049</t>
+  </si>
+  <si>
+    <t>0.0422,0.1295,0.9051,0.0172</t>
+  </si>
+  <si>
+    <t>0.0386,0.0638,0.8825,0.0947</t>
+  </si>
+  <si>
+    <t>0.0007,0.9850,0.5395,0.0003</t>
+  </si>
+  <si>
+    <t>0.0077,0.0156,0.9748,0.0383</t>
+  </si>
+  <si>
+    <t>0.0010,0.9965,0.0219,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.6451,0.0771,0.2103,0.0735</t>
+  </si>
+  <si>
+    <t>0.5926,0.1279,0.2850,0.0457</t>
+  </si>
+  <si>
+    <t>0.0021,0.6726,0.9563,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.9775,0.3806,0.0011</t>
+  </si>
+  <si>
+    <t>0.0135,0.9140,0.4848,0.0041</t>
+  </si>
+  <si>
+    <t>0.0005,0.9940,0.2150,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.9730,0.3928,0.0028</t>
+  </si>
+  <si>
+    <t>0.0034,0.0016,0.0183,0.9943</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.0007,0.9993</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0048,0.0013,0.0024,0.9965</t>
+  </si>
+  <si>
+    <t>0.0113,0.0043,0.0116,0.9893</t>
+  </si>
+  <si>
+    <t>0.0007,0.0010,0.0005,0.9995</t>
+  </si>
+  <si>
+    <t>0.0033,0.9752,0.3399,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.9831,0.4181,0.0005</t>
+  </si>
+  <si>
+    <t>0.0169,0.6570,0.8029,0.0084</t>
+  </si>
+  <si>
+    <t>0.0267,0.8728,0.3464,0.0704</t>
+  </si>
+  <si>
+    <t>0.0080,0.9482,0.3911,0.0016</t>
+  </si>
+  <si>
+    <t>0.0080,0.9578,0.2981,0.0020</t>
+  </si>
+  <si>
+    <t>0.9929,0.0002,0.0000,0.0025</t>
+  </si>
+  <si>
+    <t>0.9931,0.0024,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9902,0.0025,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9916,0.0007,0.0000,0.0022</t>
+  </si>
+  <si>
+    <t>0.9940,0.0012,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9959,0.0012,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9924,0.0018,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9942,0.0002,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.9933,0.0010,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9955,0.0003,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9958,0.0019,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0005,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0001,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.0024,0.0039,0.9929,0.0192</t>
+  </si>
+  <si>
+    <t>0.0454,0.0955,0.9160,0.0067</t>
+  </si>
+  <si>
+    <t>0.3599,0.0512,0.1405,0.4151</t>
+  </si>
+  <si>
+    <t>0.2238,0.0058,0.4803,0.2230</t>
+  </si>
+  <si>
+    <t>0.0081,0.9845,0.0131,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9936,0.0174,0.0000</t>
+  </si>
+  <si>
+    <t>0.0255,0.9684,0.0070,0.0001</t>
+  </si>
+  <si>
+    <t>0.0429,0.9452,0.0171,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.9934,0.0171,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9963,0.0070,0.0000</t>
+  </si>
+  <si>
+    <t>0.4055,0.6346,0.0128,0.0011</t>
+  </si>
+  <si>
+    <t>0.2201,0.5037,0.1296,0.3700</t>
+  </si>
+  <si>
+    <t>0.3699,0.0318,0.6157,0.0388</t>
+  </si>
+  <si>
+    <t>0.1643,0.7243,0.1708,0.1376</t>
+  </si>
+  <si>
+    <t>0.5093,0.1351,0.3395,0.0583</t>
+  </si>
+  <si>
+    <t>0.0356,0.0631,0.0199,0.9664</t>
+  </si>
+  <si>
+    <t>0.0012,0.9965,0.0164,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0098,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.9949,0.0103,0.0030</t>
+  </si>
+  <si>
+    <t>0.0002,0.9974,0.2059,0.0000</t>
+  </si>
+  <si>
+    <t>0.0122,0.9748,0.0373,0.0001</t>
+  </si>
+  <si>
+    <t>0.6562,0.3789,0.0137,0.0015</t>
+  </si>
+  <si>
+    <t>0.4173,0.6310,0.0124,0.0011</t>
+  </si>
+  <si>
+    <t>0.9678,0.0224,0.0028,0.0031</t>
+  </si>
+  <si>
+    <t>0.9927,0.0002,0.0000,0.0025</t>
+  </si>
+  <si>
+    <t>0.9903,0.0005,0.0000,0.0031</t>
+  </si>
+  <si>
+    <t>0.9899,0.0008,0.0001,0.0032</t>
+  </si>
+  <si>
+    <t>0.9920,0.0039,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9124,0.0952,0.0042,0.0023</t>
+  </si>
+  <si>
+    <t>0.9867,0.0006,0.0000,0.0045</t>
+  </si>
+  <si>
+    <t>0.9944,0.0005,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.0098,0.8451,0.7236,0.0037</t>
+  </si>
+  <si>
+    <t>0.0314,0.7812,0.6195,0.0086</t>
+  </si>
+  <si>
+    <t>0.1870,0.4565,0.4783,0.0520</t>
+  </si>
+  <si>
+    <t>0.1507,0.0875,0.7916,0.0233</t>
+  </si>
+  <si>
+    <t>0.4121,0.1446,0.1818,0.3067</t>
+  </si>
+  <si>
+    <t>0.5137,0.1758,0.2390,0.1182</t>
+  </si>
+  <si>
+    <t>0.3913,0.0144,0.2628,0.2327</t>
+  </si>
+  <si>
+    <t>0.5153,0.3152,0.0700,0.0793</t>
+  </si>
+  <si>
+    <t>0.0105,0.0025,0.0035,0.9928</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0015,0.0005,0.0016,0.9987</t>
+  </si>
+  <si>
+    <t>0.0007,0.9847,0.4827,0.0004</t>
+  </si>
+  <si>
+    <t>0.9901,0.0019,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.0245,0.9665,0.0096,0.0002</t>
+  </si>
+  <si>
+    <t>0.9737,0.0035,0.0004,0.0077</t>
+  </si>
+  <si>
+    <t>0.2576,0.7518,0.0143,0.0006</t>
+  </si>
+  <si>
+    <t>0.9641,0.0011,0.0003,0.0185</t>
+  </si>
+  <si>
+    <t>0.1381,0.0030,0.0039,0.8947</t>
+  </si>
+  <si>
+    <t>0.9935,0.0002,0.0000,0.0024</t>
+  </si>
+  <si>
+    <t>0.0305,0.2631,0.8943,0.0126</t>
+  </si>
+  <si>
+    <t>0.4742,0.0023,0.0025,0.5274</t>
+  </si>
+  <si>
+    <t>0.8678,0.0015,0.0008,0.0976</t>
+  </si>
+  <si>
+    <t>0.0765,0.9023,0.0423,0.0024</t>
+  </si>
+  <si>
+    <t>0.8711,0.0813,0.0211,0.0157</t>
+  </si>
+  <si>
+    <t>0.4424,0.5046,0.0871,0.0115</t>
+  </si>
+  <si>
+    <t>0.1767,0.7545,0.1502,0.0779</t>
+  </si>
+  <si>
+    <t>0.3450,0.4934,0.2106,0.0130</t>
+  </si>
+  <si>
+    <t>0.3935,0.4825,0.1486,0.0073</t>
+  </si>
+  <si>
+    <t>0.9938,0.0008,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9941,0.0007,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9915,0.0007,0.0000,0.0024</t>
+  </si>
+  <si>
+    <t>0.9889,0.0003,0.0000,0.0044</t>
+  </si>
+  <si>
+    <t>0.9925,0.0008,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9875,0.0009,0.0000,0.0036</t>
+  </si>
+  <si>
+    <t>0.9943,0.0002,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.2047,0.7890,0.0318,0.0014</t>
+  </si>
+  <si>
+    <t>0.7246,0.3299,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.3894,0.6736,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.5860,0.3648,0.0158,0.0196</t>
+  </si>
+  <si>
+    <t>0.9683,0.0220,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9754,0.0036,0.0003,0.0069</t>
+  </si>
+  <si>
+    <t>0.9802,0.0099,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.6639,0.4049,0.0050,0.0010</t>
+  </si>
+  <si>
+    <t>0.0014,0.0707,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.9545,0.0389,0.0017,0.0024</t>
+  </si>
+  <si>
+    <t>0.0024,0.0221,0.9932,0.0026</t>
+  </si>
+  <si>
+    <t>0.0814,0.0573,0.8828,0.0273</t>
+  </si>
+  <si>
+    <t>0.0405,0.0081,0.9613,0.0063</t>
+  </si>
+  <si>
+    <t>0.0327,0.4824,0.7929,0.0178</t>
+  </si>
+  <si>
+    <t>0.0660,0.2702,0.8146,0.0086</t>
+  </si>
+  <si>
+    <t>0.0010,0.0016,0.9978,0.0026</t>
+  </si>
+  <si>
+    <t>0.0138,0.0100,0.9794,0.0111</t>
+  </si>
+  <si>
+    <t>0.4036,0.3173,0.2920,0.0367</t>
+  </si>
+  <si>
+    <t>0.4514,0.0515,0.5404,0.0371</t>
+  </si>
+  <si>
+    <t>0.3796,0.2020,0.3724,0.0699</t>
+  </si>
+  <si>
+    <t>0.1468,0.6799,0.2771,0.0106</t>
+  </si>
+  <si>
+    <t>0.0341,0.9064,0.2320,0.0291</t>
+  </si>
+  <si>
+    <t>0.1954,0.6787,0.1977,0.0183</t>
+  </si>
+  <si>
+    <t>0.5907,0.0782,0.2414,0.0891</t>
+  </si>
+  <si>
+    <t>0.5152,0.0688,0.4085,0.0516</t>
+  </si>
+  <si>
+    <t>0.0534,0.9327,0.0149,0.0002</t>
+  </si>
+  <si>
+    <t>0.4963,0.5589,0.0087,0.0006</t>
+  </si>
+  <si>
+    <t>0.2987,0.7320,0.0128,0.0008</t>
+  </si>
+  <si>
+    <t>0.9923,0.0035,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9757,0.0239,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.4154,0.3842,0.2192,0.0324</t>
+  </si>
+  <si>
+    <t>0.5831,0.0317,0.2259,0.1188</t>
+  </si>
+  <si>
+    <t>0.3723,0.0777,0.1470,0.3812</t>
+  </si>
+  <si>
+    <t>0.5329,0.0664,0.3616,0.0778</t>
+  </si>
+  <si>
+    <t>0.4211,0.1719,0.3535,0.0819</t>
+  </si>
+  <si>
+    <t>0.0079,0.0238,0.9736,0.0388</t>
+  </si>
+  <si>
+    <t>0.0704,0.0454,0.7982,0.1808</t>
+  </si>
+  <si>
+    <t>0.2036,0.2886,0.4890,0.1681</t>
+  </si>
+  <si>
+    <t>0.4229,0.0387,0.5458,0.0578</t>
+  </si>
+  <si>
+    <t>0.1067,0.2393,0.7375,0.0378</t>
+  </si>
+  <si>
+    <t>0.9900,0.0008,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.9894,0.0007,0.0000,0.0030</t>
+  </si>
+  <si>
+    <t>0.9910,0.0026,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9945,0.0014,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9943,0.0009,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9923,0.0008,0.0000,0.0019</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9899,0.0005,0.0000,0.0032</t>
+  </si>
+  <si>
+    <t>0.0939,0.1577,0.8332,0.0079</t>
+  </si>
+  <si>
+    <t>0.1007,0.8570,0.0983,0.0049</t>
+  </si>
+  <si>
+    <t>0.8444,0.0862,0.0471,0.0138</t>
+  </si>
+  <si>
+    <t>0.0144,0.0109,0.9788,0.0087</t>
+  </si>
+  <si>
+    <t>0.0041,0.0556,0.9826,0.0092</t>
+  </si>
+  <si>
+    <t>0.2919,0.1743,0.5639,0.0296</t>
+  </si>
+  <si>
+    <t>0.0007,0.0018,0.9975,0.0083</t>
+  </si>
+  <si>
+    <t>0.0691,0.1020,0.8767,0.0088</t>
+  </si>
+  <si>
+    <t>0.0036,0.0149,0.9830,0.0300</t>
+  </si>
+  <si>
+    <t>0.0430,0.0093,0.8049,0.3112</t>
+  </si>
+  <si>
+    <t>0.1797,0.5504,0.3349,0.1041</t>
+  </si>
+  <si>
+    <t>0.3327,0.1159,0.3527,0.2398</t>
+  </si>
+  <si>
+    <t>0.4289,0.0528,0.2328,0.2628</t>
+  </si>
+  <si>
+    <t>0.1271,0.0189,0.0439,0.8645</t>
+  </si>
+  <si>
+    <t>0.9950,0.0008,0.0000,0.0010</t>
   </si>
   <si>
     <t>0.9941,0.0005,0.0000,0.0015</t>
   </si>
   <si>
-    <t>0.0112,0.9267,0.4439,0.0145</t>
-  </si>
-  <si>
-    <t>0.0155,0.8005,0.7259,0.0042</t>
-  </si>
-  <si>
-    <t>0.0374,0.0500,0.9175,0.0430</t>
-  </si>
-  <si>
-    <t>0.2210,0.1034,0.6969,0.0419</t>
-  </si>
-  <si>
-    <t>0.3414,0.0818,0.0990,0.4979</t>
-  </si>
-  <si>
-    <t>0.6158,0.0725,0.2862,0.0567</t>
-  </si>
-  <si>
-    <t>0.3888,0.0109,0.4543,0.1119</t>
-  </si>
-  <si>
-    <t>0.6154,0.1804,0.1648,0.0501</t>
-  </si>
-  <si>
-    <t>0.0173,0.0051,0.0172,0.9822</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0023,0.0010,0.0054,0.9974</t>
-  </si>
-  <si>
-    <t>0.0021,0.9669,0.5332,0.0012</t>
-  </si>
-  <si>
-    <t>0.9915,0.0003,0.0000,0.0027</t>
-  </si>
-  <si>
-    <t>0.1368,0.8747,0.0060,0.0003</t>
-  </si>
-  <si>
-    <t>0.9719,0.0013,0.0001,0.0116</t>
-  </si>
-  <si>
-    <t>0.1523,0.8390,0.0139,0.0004</t>
-  </si>
-  <si>
-    <t>0.9875,0.0006,0.0001,0.0047</t>
-  </si>
-  <si>
-    <t>0.0165,0.0020,0.0013,0.9897</t>
-  </si>
-  <si>
-    <t>0.9893,0.0003,0.0000,0.0044</t>
-  </si>
-  <si>
-    <t>0.0326,0.5583,0.7942,0.0112</t>
-  </si>
-  <si>
-    <t>0.7313,0.0037,0.0060,0.1865</t>
-  </si>
-  <si>
-    <t>0.9078,0.0046,0.0027,0.0455</t>
-  </si>
-  <si>
-    <t>0.1035,0.8699,0.0496,0.0029</t>
-  </si>
-  <si>
-    <t>0.5916,0.3970,0.0350,0.0061</t>
-  </si>
-  <si>
-    <t>0.6261,0.2896,0.0968,0.0146</t>
-  </si>
-  <si>
-    <t>0.3638,0.3685,0.1002,0.2054</t>
-  </si>
-  <si>
-    <t>0.3442,0.4831,0.2340,0.0152</t>
-  </si>
-  <si>
-    <t>0.4795,0.4619,0.0707,0.0057</t>
-  </si>
-  <si>
-    <t>0.9939,0.0005,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9905,0.0007,0.0000,0.0027</t>
-  </si>
-  <si>
-    <t>0.9943,0.0005,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9882,0.0003,0.0000,0.0046</t>
-  </si>
-  <si>
-    <t>0.9929,0.0008,0.0000,0.0017</t>
-  </si>
-  <si>
-    <t>0.9926,0.0008,0.0000,0.0018</t>
-  </si>
-  <si>
-    <t>0.9909,0.0003,0.0000,0.0031</t>
-  </si>
-  <si>
-    <t>0.1600,0.8289,0.0341,0.0019</t>
-  </si>
-  <si>
-    <t>0.6849,0.4001,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.1927,0.8229,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.0807,0.3562,0.7736,0.0062</t>
-  </si>
-  <si>
-    <t>0.9793,0.0114,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9644,0.0042,0.0004,0.0112</t>
-  </si>
-  <si>
-    <t>0.9786,0.0153,0.0012,0.0020</t>
-  </si>
-  <si>
-    <t>0.5387,0.4737,0.0213,0.0015</t>
-  </si>
-  <si>
-    <t>0.0004,0.0186,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.9712,0.0169,0.0012,0.0030</t>
-  </si>
-  <si>
-    <t>0.0028,0.0183,0.9928,0.0025</t>
-  </si>
-  <si>
-    <t>0.0765,0.3143,0.7658,0.0259</t>
-  </si>
-  <si>
-    <t>0.0285,0.0124,0.9704,0.0047</t>
-  </si>
-  <si>
-    <t>0.0284,0.3847,0.8550,0.0109</t>
-  </si>
-  <si>
-    <t>0.0644,0.1191,0.8751,0.0146</t>
-  </si>
-  <si>
-    <t>0.0067,0.0037,0.9899,0.0059</t>
-  </si>
-  <si>
-    <t>0.1252,0.0128,0.8481,0.0461</t>
-  </si>
-  <si>
-    <t>0.5025,0.0444,0.4592,0.0480</t>
-  </si>
-  <si>
-    <t>0.4203,0.0778,0.5560,0.0189</t>
-  </si>
-  <si>
-    <t>0.5182,0.2622,0.1992,0.0553</t>
-  </si>
-  <si>
-    <t>0.5197,0.2313,0.2577,0.0395</t>
-  </si>
-  <si>
-    <t>0.3675,0.1740,0.4658,0.0172</t>
-  </si>
-  <si>
-    <t>0.4873,0.0938,0.4351,0.0256</t>
-  </si>
-  <si>
-    <t>0.5428,0.1356,0.2024,0.1198</t>
-  </si>
-  <si>
-    <t>0.5514,0.1681,0.2755,0.0376</t>
-  </si>
-  <si>
-    <t>0.0476,0.9429,0.0089,0.0001</t>
-  </si>
-  <si>
-    <t>0.2675,0.7753,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.9360,0.0684,0.0011,0.0014</t>
-  </si>
-  <si>
-    <t>0.9667,0.0420,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.6111,0.4814,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.4411,0.2886,0.1864,0.1613</t>
-  </si>
-  <si>
-    <t>0.5269,0.2695,0.1761,0.0713</t>
-  </si>
-  <si>
-    <t>0.0394,0.0717,0.0121,0.9678</t>
-  </si>
-  <si>
-    <t>0.5484,0.0517,0.3015,0.1074</t>
-  </si>
-  <si>
-    <t>0.2984,0.0990,0.5856,0.0394</t>
-  </si>
-  <si>
-    <t>0.0015,0.0118,0.9944,0.0075</t>
-  </si>
-  <si>
-    <t>0.0979,0.0787,0.5390,0.4259</t>
-  </si>
-  <si>
-    <t>0.1280,0.2364,0.7293,0.0265</t>
-  </si>
-  <si>
-    <t>0.3141,0.1247,0.6005,0.0390</t>
-  </si>
-  <si>
-    <t>0.0903,0.2680,0.7523,0.0219</t>
-  </si>
-  <si>
-    <t>0.9933,0.0004,0.0000,0.0019</t>
-  </si>
-  <si>
-    <t>0.9931,0.0007,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9862,0.0011,0.0000,0.0039</t>
-  </si>
-  <si>
-    <t>0.9952,0.0009,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9935,0.0013,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9953,0.0010,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9955,0.0002,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9868,0.0018,0.0001,0.0033</t>
-  </si>
-  <si>
-    <t>0.2500,0.0485,0.7528,0.0138</t>
-  </si>
-  <si>
-    <t>0.3274,0.6211,0.0949,0.0284</t>
-  </si>
-  <si>
-    <t>0.4979,0.0967,0.2055,0.1747</t>
-  </si>
-  <si>
-    <t>0.0059,0.0144,0.9888,0.0047</t>
-  </si>
-  <si>
-    <t>0.0040,0.1190,0.9773,0.0064</t>
-  </si>
-  <si>
-    <t>0.1960,0.0606,0.7316,0.0492</t>
-  </si>
-  <si>
-    <t>0.0012,0.0046,0.9971,0.0029</t>
-  </si>
-  <si>
-    <t>0.0464,0.0645,0.9246,0.0099</t>
-  </si>
-  <si>
-    <t>0.0046,0.0088,0.9907,0.0063</t>
-  </si>
-  <si>
-    <t>0.1683,0.0969,0.6765,0.1683</t>
-  </si>
-  <si>
-    <t>0.1716,0.5833,0.2560,0.1873</t>
-  </si>
-  <si>
-    <t>0.0990,0.0854,0.1225,0.8471</t>
-  </si>
-  <si>
-    <t>0.2200,0.1183,0.6175,0.1037</t>
-  </si>
-  <si>
-    <t>0.2688,0.0244,0.0780,0.6253</t>
-  </si>
-  <si>
-    <t>0.9940,0.0009,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9901,0.0016,0.0001,0.0021</t>
-  </si>
-  <si>
-    <t>0.9958,0.0004,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9926,0.0025,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9964,0.0003,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9933,0.0019,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9915,0.0039,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9954,0.0010,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.3097,0.1465,0.5141,0.1153</t>
-  </si>
-  <si>
-    <t>0.0017,0.3879,0.9712,0.0016</t>
-  </si>
-  <si>
-    <t>0.0407,0.0631,0.8968,0.0762</t>
-  </si>
-  <si>
-    <t>0.4387,0.1289,0.4084,0.0601</t>
-  </si>
-  <si>
-    <t>0.0130,0.0170,0.9672,0.0392</t>
-  </si>
-  <si>
-    <t>0.0554,0.0083,0.8362,0.2019</t>
-  </si>
-  <si>
-    <t>0.2694,0.0821,0.2420,0.4620</t>
-  </si>
-  <si>
-    <t>0.1783,0.0394,0.6187,0.2349</t>
-  </si>
-  <si>
-    <t>0.5540,0.0058,0.0115,0.3782</t>
-  </si>
-  <si>
-    <t>0.0045,0.0100,0.0034,0.9962</t>
-  </si>
-  <si>
-    <t>0.0041,0.0010,0.0026,0.9967</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.0014,0.9992</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.0005,0.9995</t>
-  </si>
-  <si>
-    <t>0.0748,0.0204,0.0115,0.9396</t>
+    <t>0.9954,0.0004,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9953,0.0019,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9914,0.0038,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9943,0.0018,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.1094,0.1746,0.7748,0.0221</t>
+  </si>
+  <si>
+    <t>0.0041,0.1442,0.9785,0.0035</t>
+  </si>
+  <si>
+    <t>0.1088,0.1520,0.8080,0.0322</t>
+  </si>
+  <si>
+    <t>0.2225,0.5015,0.3549,0.0368</t>
+  </si>
+  <si>
+    <t>0.0538,0.3219,0.7012,0.1171</t>
+  </si>
+  <si>
+    <t>0.1257,0.0098,0.8531,0.0429</t>
+  </si>
+  <si>
+    <t>0.4728,0.0915,0.3912,0.0928</t>
+  </si>
+  <si>
+    <t>0.2330,0.0582,0.6852,0.0851</t>
+  </si>
+  <si>
+    <t>0.3470,0.0115,0.0159,0.6235</t>
+  </si>
+  <si>
+    <t>0.0058,0.0038,0.0017,0.9962</t>
+  </si>
+  <si>
+    <t>0.0034,0.0009,0.0013,0.9977</t>
+  </si>
+  <si>
+    <t>0.0013,0.0005,0.0029,0.9986</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.1593,0.0734,0.0118,0.8244</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1964,7 +1970,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1975,10 +1981,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1992,7 +1998,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2006,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2020,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2034,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2048,7 +2054,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2062,7 +2068,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2076,7 +2082,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2090,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2104,7 +2110,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2115,10 +2121,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2132,7 +2138,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2143,10 +2149,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2160,7 +2166,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2171,10 +2177,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2188,7 +2194,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2202,7 +2208,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2216,7 +2222,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2230,7 +2236,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2244,7 +2250,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2255,10 +2261,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2269,10 +2275,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2286,7 +2292,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2297,10 +2303,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2314,7 +2320,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2328,7 +2334,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2342,7 +2348,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,7 +2376,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2384,7 +2390,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2395,10 +2401,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2412,7 +2418,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2423,10 +2429,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2437,10 +2443,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2454,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,7 +2474,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2482,7 +2488,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2496,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2510,7 +2516,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2524,7 +2530,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2538,7 +2544,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2552,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2563,10 +2569,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2580,7 +2586,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2594,7 +2600,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2608,7 +2614,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2622,7 +2628,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2633,10 +2639,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2650,7 +2656,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2664,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2678,7 +2684,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2692,7 +2698,7 @@
         <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2706,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2720,7 +2726,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2734,7 +2740,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2748,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2762,7 +2768,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2776,7 +2782,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2790,7 +2796,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2804,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2818,7 +2824,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2832,7 +2838,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2846,7 +2852,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2860,7 +2866,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2874,7 +2880,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2888,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2899,10 +2905,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,7 +2922,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2927,10 +2933,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2941,10 +2947,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,7 +2964,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2972,7 +2978,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2986,7 +2992,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3000,7 +3006,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3014,7 +3020,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3028,7 +3034,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3042,7 +3048,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3056,7 +3062,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3070,7 +3076,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3084,7 +3090,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3098,7 +3104,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3109,10 +3115,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3123,10 +3129,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3137,10 +3143,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3154,7 +3160,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3168,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3182,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3196,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3210,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3224,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3238,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3252,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3266,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3280,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3294,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>272</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3308,7 +3314,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3322,7 +3328,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3336,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3350,7 +3356,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3364,7 +3370,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3378,7 +3384,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3392,7 +3398,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3406,7 +3412,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3417,10 +3423,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3431,10 +3437,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3448,7 +3454,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3462,7 +3468,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3476,7 +3482,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3490,7 +3496,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3504,7 +3510,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3518,7 +3524,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3532,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3543,10 +3549,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3560,7 +3566,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,7 +3580,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3585,10 +3591,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3602,7 +3608,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3616,7 +3622,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3630,7 +3636,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3644,7 +3650,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3658,7 +3664,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3672,7 +3678,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3686,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3700,7 +3706,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3714,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3728,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3742,7 +3748,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3756,7 +3762,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3770,7 +3776,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3784,7 +3790,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3798,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3812,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3823,10 +3829,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3840,7 +3846,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3851,10 +3857,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3868,7 +3874,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3879,10 +3885,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,7 +3902,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3907,10 +3913,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3924,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3938,7 +3944,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3952,7 +3958,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3966,7 +3972,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3980,7 +3986,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3991,10 +3997,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4008,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,7 +4028,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4036,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4050,7 +4056,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4064,7 +4070,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,7 +4084,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4092,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4103,10 +4109,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4117,10 +4123,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4134,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,7 +4154,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4162,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4173,10 +4179,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4187,10 +4193,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4201,10 +4207,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4215,10 +4221,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4232,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4246,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4260,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4274,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4288,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4302,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4316,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4330,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4344,7 +4350,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4372,7 +4378,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4383,10 +4389,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4400,7 +4406,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4414,7 +4420,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4428,7 +4434,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4442,7 +4448,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4456,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4470,7 +4476,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4484,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4498,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4512,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4526,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4540,7 +4546,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4554,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4568,7 +4574,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4579,10 +4585,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4607,10 +4613,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4621,10 +4627,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4635,10 +4641,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4649,10 +4655,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,7 +4672,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4694,7 +4700,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4708,7 +4714,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4719,10 +4725,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4736,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4750,7 +4756,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4761,10 +4767,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4778,7 +4784,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4789,10 +4795,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,7 +4812,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4817,10 +4823,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4834,7 +4840,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4848,7 +4854,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4859,10 +4865,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4876,7 +4882,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4890,7 +4896,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4904,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4918,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4932,7 +4938,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4946,7 +4952,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4960,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4974,7 +4980,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4988,7 +4994,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5002,7 +5008,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5016,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5030,7 +5036,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5044,7 +5050,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5058,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5072,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5086,7 +5092,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5100,7 +5106,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5114,7 +5120,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5128,7 +5134,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5142,7 +5148,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5156,7 +5162,7 @@
         <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5167,10 +5173,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5181,10 +5187,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5198,7 +5204,7 @@
         <v>260</v>
       </c>
       <c r="D234" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5212,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5226,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5240,7 +5246,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5254,7 +5260,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5268,7 +5274,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5282,7 +5288,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5296,7 +5302,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5310,7 +5316,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5324,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5338,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5352,7 +5358,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5363,10 +5369,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5380,7 +5386,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,7 +5400,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5405,10 +5411,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5422,7 +5428,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5433,10 +5439,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5450,7 +5456,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5464,7 +5470,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5478,7 +5484,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5492,7 +5498,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5506,7 +5512,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
